--- a/data/densidad de esporas procesar.xlsx
+++ b/data/densidad de esporas procesar.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fvygh\Documents\TESIS_PREGRADO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fvygh\Documents\TESIS_PREGRADO\TESIS-DE-PREGRADO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42679B30-CC24-41AE-8EB4-EC4AA75AAE6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469CE1A0-5662-45EC-A9B9-82F06E0A5E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total_por_accesion" sheetId="1" r:id="rId1"/>
+    <sheet name="Control de correcciones" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="58">
   <si>
     <t>Grupo</t>
   </si>
@@ -170,6 +170,45 @@
   </si>
   <si>
     <t>CT32</t>
+  </si>
+  <si>
+    <t>Control de validación</t>
+  </si>
+  <si>
+    <t>Detalle</t>
+  </si>
+  <si>
+    <t>Archivo de referencia</t>
+  </si>
+  <si>
+    <t>base de datos ordenada para procesar(10).xlsx, hoja fb</t>
+  </si>
+  <si>
+    <t>Accesiones cotejadas</t>
+  </si>
+  <si>
+    <t>Único conteo total corregido</t>
+  </si>
+  <si>
+    <t>CT01: 218 → 246 esporas</t>
+  </si>
+  <si>
+    <t>Criterio de densidad</t>
+  </si>
+  <si>
+    <t>Total de esporas / 6 g (3 submuestras de 2 g)</t>
+  </si>
+  <si>
+    <t>Promedio por submuestra</t>
+  </si>
+  <si>
+    <t>Total de esporas / 3, redondeado</t>
+  </si>
+  <si>
+    <t>Fuente del total</t>
+  </si>
+  <si>
+    <t>Suma de la columna cantidad, agrupada por accesión</t>
   </si>
 </sst>
 </file>
@@ -188,7 +227,7 @@
       <name val="Carlito"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -197,12 +236,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor rgb="FF125B70"/>
       </patternFill>
     </fill>
   </fills>
@@ -218,20 +252,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -447,27 +480,27 @@
   <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="33.950000000000003" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -484,13 +517,13 @@
       <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>385</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <f t="shared" ref="F2:F36" si="0">ROUND(E2/3,0)</f>
         <v>128</v>
       </c>
@@ -505,13 +538,13 @@
       <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>1561</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <f t="shared" si="0"/>
         <v>520</v>
       </c>
@@ -526,13 +559,13 @@
       <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>843</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <f t="shared" si="0"/>
         <v>281</v>
       </c>
@@ -547,13 +580,13 @@
       <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>1945</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <f t="shared" si="0"/>
         <v>648</v>
       </c>
@@ -568,13 +601,13 @@
       <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>399</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
@@ -589,13 +622,13 @@
       <c r="C7" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>775</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="2">
         <f t="shared" si="0"/>
         <v>258</v>
       </c>
@@ -610,13 +643,13 @@
       <c r="C8" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>587</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="2">
         <f t="shared" si="0"/>
         <v>196</v>
       </c>
@@ -631,13 +664,13 @@
       <c r="C9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>530</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <f t="shared" si="0"/>
         <v>177</v>
       </c>
@@ -652,13 +685,13 @@
       <c r="C10" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>293</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <f t="shared" si="0"/>
         <v>98</v>
       </c>
@@ -673,13 +706,13 @@
       <c r="C11" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>647</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <f t="shared" si="0"/>
         <v>216</v>
       </c>
@@ -694,13 +727,13 @@
       <c r="C12" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>360</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="2">
         <f t="shared" si="0"/>
         <v>120</v>
       </c>
@@ -715,13 +748,13 @@
       <c r="C13" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>259</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
@@ -736,36 +769,36 @@
       <c r="C14" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14" s="2">
         <v>339</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="2" t="s">
+    <row r="15" spans="1:6" s="5" customFormat="1">
+      <c r="A15" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="3">
-        <v>218</v>
-      </c>
-      <c r="F15" s="3">
-        <f t="shared" si="0"/>
-        <v>73</v>
+      <c r="E15" s="2">
+        <v>246</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="0"/>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -778,13 +811,13 @@
       <c r="C16" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16" s="2">
         <v>1620</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <f t="shared" si="0"/>
         <v>540</v>
       </c>
@@ -799,13 +832,13 @@
       <c r="C17" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="3">
+      <c r="E17" s="2">
         <v>1515</v>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="2">
         <f t="shared" si="0"/>
         <v>505</v>
       </c>
@@ -820,13 +853,13 @@
       <c r="C18" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="3">
+      <c r="E18" s="2">
         <v>849</v>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="2">
         <f t="shared" si="0"/>
         <v>283</v>
       </c>
@@ -841,13 +874,13 @@
       <c r="C19" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="3">
+      <c r="E19" s="2">
         <v>1180</v>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="2">
         <f t="shared" si="0"/>
         <v>393</v>
       </c>
@@ -862,13 +895,13 @@
       <c r="C20" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="3">
+      <c r="E20" s="2">
         <v>1039</v>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="2">
         <f t="shared" si="0"/>
         <v>346</v>
       </c>
@@ -883,13 +916,13 @@
       <c r="C21" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="2">
         <v>465</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="2">
         <f t="shared" si="0"/>
         <v>155</v>
       </c>
@@ -904,13 +937,13 @@
       <c r="C22" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="2">
         <v>493</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <f t="shared" si="0"/>
         <v>164</v>
       </c>
@@ -925,13 +958,13 @@
       <c r="C23" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E23" s="3">
+      <c r="E23" s="2">
         <v>315</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="2">
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
@@ -946,13 +979,13 @@
       <c r="C24" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="2">
         <v>766</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="2">
         <f t="shared" si="0"/>
         <v>255</v>
       </c>
@@ -967,13 +1000,13 @@
       <c r="C25" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E25" s="3">
+      <c r="E25" s="2">
         <v>527</v>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="2">
         <f t="shared" si="0"/>
         <v>176</v>
       </c>
@@ -988,13 +1021,13 @@
       <c r="C26" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E26" s="3">
+      <c r="E26" s="2">
         <v>712</v>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="2">
         <f t="shared" si="0"/>
         <v>237</v>
       </c>
@@ -1009,13 +1042,13 @@
       <c r="C27" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E27" s="3">
+      <c r="E27" s="2">
         <v>944</v>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="2">
         <f t="shared" si="0"/>
         <v>315</v>
       </c>
@@ -1030,13 +1063,13 @@
       <c r="C28" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="2">
         <v>976</v>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="2">
         <f t="shared" si="0"/>
         <v>325</v>
       </c>
@@ -1051,13 +1084,13 @@
       <c r="C29" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="2">
         <v>724</v>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="2">
         <f t="shared" si="0"/>
         <v>241</v>
       </c>
@@ -1072,13 +1105,13 @@
       <c r="C30" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E30" s="2">
         <v>888</v>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="2">
         <f t="shared" si="0"/>
         <v>296</v>
       </c>
@@ -1093,13 +1126,13 @@
       <c r="C31" t="s">
         <v>8</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E31" s="2">
         <v>710</v>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="2">
         <f t="shared" si="0"/>
         <v>237</v>
       </c>
@@ -1114,13 +1147,13 @@
       <c r="C32" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E32" s="2">
         <v>783</v>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="2">
         <f t="shared" si="0"/>
         <v>261</v>
       </c>
@@ -1135,13 +1168,13 @@
       <c r="C33" t="s">
         <v>8</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E33" s="2">
         <v>522</v>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="2">
         <f t="shared" si="0"/>
         <v>174</v>
       </c>
@@ -1156,13 +1189,13 @@
       <c r="C34" t="s">
         <v>8</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="2">
         <v>448</v>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="2">
         <f t="shared" si="0"/>
         <v>149</v>
       </c>
@@ -1177,13 +1210,13 @@
       <c r="C35" t="s">
         <v>8</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="2">
         <v>545</v>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="2">
         <f t="shared" si="0"/>
         <v>182</v>
       </c>
@@ -1198,15 +1231,85 @@
       <c r="C36" t="s">
         <v>8</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="D36" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="2">
         <v>471</v>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="2">
         <f t="shared" si="0"/>
         <v>157</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="68" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="26.1" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/data/densidad de esporas procesar.xlsx
+++ b/data/densidad de esporas procesar.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fvygh\Documents\TESIS_PREGRADO\TESIS-DE-PREGRADO\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469CE1A0-5662-45EC-A9B9-82F06E0A5E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16963228-FCE3-4CDF-9A87-22663243D103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="15375" windowHeight="7785" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total_por_accesion" sheetId="1" r:id="rId1"/>
